--- a/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultiplesheets.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultiplesheets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet1" sheetId="1" r:id="R5c9df10abe0146d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet2" sheetId="2" r:id="Rd050ae55202347da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet1" sheetId="1" r:id="R75b12b2a68b640f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet2" sheetId="2" r:id="R622d238b79cd4e33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,8 +189,8 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a18123c2cd4e4e"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R533e3f5f839d4f40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ed7e1388e44255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f4a21208d4b40db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -216,7 +216,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08ae36acb6e44197"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e9d472bbac4177"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultiplesheets.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultiplesheets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet1" sheetId="1" r:id="R75b12b2a68b640f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet2" sheetId="2" r:id="R622d238b79cd4e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet1" sheetId="1" r:id="Rcb66447cfd064131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet2" sheetId="2" r:id="R9e2117b72e1949aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,8 +189,8 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ed7e1388e44255"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f4a21208d4b40db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6319541f49604563"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d12b46460904023"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -216,7 +216,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e9d472bbac4177"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fdd57b379ff423b"/>
   </x:tableParts>
 </x:worksheet>
 </file>